--- a/stage_2_scheduling/output/table.xlsx
+++ b/stage_2_scheduling/output/table.xlsx
@@ -651,7 +651,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 19</t>
+          <t>Сотрудник 59</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 20</t>
+          <t>Сотрудник 3</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 31</t>
+          <t>Сотрудник 1</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 44</t>
+          <t>Сотрудник 15</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
@@ -1839,9 +1839,7 @@
       <c r="K31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="7" t="inlineStr"/>
@@ -1864,12 +1862,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
@@ -1894,9 +1892,7 @@
       <c r="L32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M32" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr"/>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr"/>
@@ -2048,7 +2044,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 59</t>
+          <t>Сотрудник 43</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2104,12 +2100,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 15</t>
+          <t>Сотрудник 44</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2119,7 +2115,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr"/>
@@ -2129,7 +2125,9 @@
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
+      <c r="L37" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M37" s="6" t="n">
         <v>1</v>
       </c>
@@ -2158,7 +2156,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 17</t>
+          <t>Сотрудник 31</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2212,12 +2210,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 1</t>
+          <t>Сотрудник 52</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2227,7 +2225,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr"/>
@@ -2238,7 +2236,9 @@
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" s="6" t="n">
         <v>1</v>
       </c>
@@ -2264,7 +2264,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 11</t>
+          <t>Сотрудник 17</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 54</t>
+          <t>Сотрудник 7</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 3</t>
+          <t>Сотрудник 20</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 36</t>
+          <t>Сотрудник 44</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 31</t>
+          <t>Сотрудник 32</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
@@ -2964,10 +2964,18 @@
       <c r="G57" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+      <c r="H57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
@@ -2981,7 +2989,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 32</t>
+          <t>Сотрудник 43</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -2991,12 +2999,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
@@ -3008,18 +3016,10 @@
       <c r="G58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="7" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 19</t>
+          <t>Сотрудник 38</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -3131,7 +3131,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 38</t>
+          <t>Сотрудник 45</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 45</t>
+          <t>Сотрудник 47</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 16</t>
+          <t>Сотрудник 39</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 47</t>
+          <t>Сотрудник 19</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -3913,7 +3913,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 8</t>
+          <t>Сотрудник 7</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
@@ -3952,9 +3952,7 @@
       <c r="K80" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L80" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="7" t="inlineStr"/>
@@ -3967,7 +3965,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 28</t>
+          <t>Сотрудник 17</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -3977,12 +3975,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
@@ -4006,7 +4004,9 @@
       <c r="K81" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L81" s="7" t="inlineStr"/>
+      <c r="L81" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 44</t>
+          <t>Сотрудник 28</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
@@ -4058,12 +4058,8 @@
       <c r="K82" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L82" s="7" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr"/>
       <c r="O82" s="7" t="inlineStr"/>
       <c r="P82" s="7" t="inlineStr"/>
@@ -4075,7 +4071,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 4</t>
+          <t>Сотрудник 8</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4181,7 +4177,7 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 17</t>
+          <t>Сотрудник 1</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -4191,12 +4187,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr"/>
@@ -4225,9 +4221,7 @@
       <c r="P85" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q85" s="7" t="inlineStr"/>
       <c r="R85" s="7" t="inlineStr"/>
       <c r="S85" s="7" t="inlineStr"/>
       <c r="T85" s="7" t="inlineStr"/>
@@ -4235,7 +4229,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 52</t>
+          <t>Сотрудник 4</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -4245,12 +4239,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr"/>
@@ -4279,7 +4273,9 @@
       <c r="P86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" s="7" t="inlineStr"/>
+      <c r="Q86" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R86" s="7" t="inlineStr"/>
       <c r="S86" s="7" t="inlineStr"/>
       <c r="T86" s="7" t="inlineStr"/>
@@ -4287,12 +4283,12 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 43</t>
+          <t>Сотрудник 31</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4302,7 +4298,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr"/>
@@ -4312,7 +4308,9 @@
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr"/>
       <c r="K87" s="7" t="inlineStr"/>
-      <c r="L87" s="7" t="inlineStr"/>
+      <c r="L87" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M87" s="6" t="n">
         <v>1</v>
       </c>
@@ -4341,12 +4339,12 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 54</t>
+          <t>Сотрудник 59</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -4356,7 +4354,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr"/>
@@ -4367,7 +4365,9 @@
       <c r="J88" s="7" t="inlineStr"/>
       <c r="K88" s="7" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr"/>
-      <c r="M88" s="7" t="inlineStr"/>
+      <c r="M88" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N88" s="6" t="n">
         <v>1</v>
       </c>
@@ -4445,7 +4445,7 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 11</t>
+          <t>Сотрудник 14</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 14</t>
+          <t>Сотрудник 52</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 2</t>
+          <t>Сотрудник 54</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 15</t>
+          <t>Сотрудник 36</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 8</t>
+          <t>Сотрудник 54</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -5158,7 +5158,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 19</t>
+          <t>Сотрудник 8</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 22</t>
+          <t>Сотрудник 38</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 51</t>
+          <t>Сотрудник 45</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 47</t>
+          <t>Сотрудник 19</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E123" s="6" t="n">
@@ -5855,9 +5855,7 @@
       <c r="L123" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M123" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="7" t="inlineStr"/>
       <c r="O123" s="7" t="inlineStr"/>
       <c r="P123" s="7" t="inlineStr"/>
@@ -5869,12 +5867,12 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 3</t>
+          <t>Сотрудник 2</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -5884,7 +5882,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
@@ -5895,7 +5893,9 @@
       <c r="J124" s="7" t="inlineStr"/>
       <c r="K124" s="7" t="inlineStr"/>
       <c r="L124" s="7" t="inlineStr"/>
-      <c r="M124" s="7" t="inlineStr"/>
+      <c r="M124" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N124" s="6" t="n">
         <v>1</v>
       </c>
@@ -6056,7 +6056,7 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 14</t>
+          <t>Сотрудник 15</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E129" s="6" t="n">
@@ -6098,9 +6098,7 @@
       <c r="L129" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M129" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="7" t="inlineStr"/>
       <c r="O129" s="7" t="inlineStr"/>
       <c r="P129" s="7" t="inlineStr"/>
@@ -6112,7 +6110,7 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 31</t>
+          <t>Сотрудник 28</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -6122,12 +6120,12 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E130" s="6" t="n">
@@ -6151,12 +6149,8 @@
       <c r="K130" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L130" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M130" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L130" s="7" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
       <c r="N130" s="7" t="inlineStr"/>
       <c r="O130" s="7" t="inlineStr"/>
       <c r="P130" s="7" t="inlineStr"/>
@@ -6168,7 +6162,7 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 44</t>
+          <t>Сотрудник 52</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -6178,12 +6172,12 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E131" s="6" t="n">
@@ -6207,8 +6201,12 @@
       <c r="K131" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L131" s="7" t="inlineStr"/>
-      <c r="M131" s="7" t="inlineStr"/>
+      <c r="L131" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N131" s="7" t="inlineStr"/>
       <c r="O131" s="7" t="inlineStr"/>
       <c r="P131" s="7" t="inlineStr"/>
@@ -6220,7 +6218,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 54</t>
+          <t>Сотрудник 59</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -6324,7 +6322,7 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 59</t>
+          <t>Сотрудник 51</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -6334,12 +6332,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
@@ -6356,21 +6354,11 @@
       <c r="L134" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M134" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N134" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P134" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M134" s="7" t="inlineStr"/>
+      <c r="N134" s="7" t="inlineStr"/>
+      <c r="O134" s="7" t="inlineStr"/>
+      <c r="P134" s="7" t="inlineStr"/>
+      <c r="Q134" s="7" t="inlineStr"/>
       <c r="R134" s="7" t="inlineStr"/>
       <c r="S134" s="7" t="inlineStr"/>
       <c r="T134" s="7" t="inlineStr"/>
@@ -6378,7 +6366,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 45</t>
+          <t>Сотрудник 31</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -6388,12 +6376,12 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
@@ -6411,10 +6399,18 @@
       <c r="M135" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N135" s="7" t="inlineStr"/>
-      <c r="O135" s="7" t="inlineStr"/>
-      <c r="P135" s="7" t="inlineStr"/>
-      <c r="Q135" s="7" t="inlineStr"/>
+      <c r="N135" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q135" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R135" s="7" t="inlineStr"/>
       <c r="S135" s="7" t="inlineStr"/>
       <c r="T135" s="7" t="inlineStr"/>
@@ -6422,7 +6418,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 17</t>
+          <t>Сотрудник 4</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -6476,12 +6472,12 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 4</t>
+          <t>Сотрудник 11</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
@@ -6491,7 +6487,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
@@ -6502,7 +6498,9 @@
       <c r="J137" s="7" t="inlineStr"/>
       <c r="K137" s="7" t="inlineStr"/>
       <c r="L137" s="7" t="inlineStr"/>
-      <c r="M137" s="7" t="inlineStr"/>
+      <c r="M137" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N137" s="6" t="n">
         <v>1</v>
       </c>
@@ -6528,12 +6526,12 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 15</t>
+          <t>Сотрудник 17</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -6543,7 +6541,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
@@ -6554,7 +6552,9 @@
       <c r="J138" s="7" t="inlineStr"/>
       <c r="K138" s="7" t="inlineStr"/>
       <c r="L138" s="7" t="inlineStr"/>
-      <c r="M138" s="7" t="inlineStr"/>
+      <c r="M138" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N138" s="6" t="n">
         <v>1</v>
       </c>
@@ -6580,7 +6580,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 43</t>
+          <t>Сотрудник 14</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -6632,7 +6632,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 52</t>
+          <t>Сотрудник 43</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -6817,7 +6817,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 28</t>
+          <t>Сотрудник 47</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E145" s="6" t="n">
@@ -6859,7 +6859,9 @@
       <c r="L145" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M145" s="7" t="inlineStr"/>
+      <c r="M145" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N145" s="7" t="inlineStr"/>
       <c r="O145" s="7" t="inlineStr"/>
       <c r="P145" s="7" t="inlineStr"/>
@@ -6871,12 +6873,12 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 7</t>
+          <t>Сотрудник 3</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -6886,7 +6888,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr"/>
@@ -6897,9 +6899,7 @@
       <c r="J146" s="7" t="inlineStr"/>
       <c r="K146" s="7" t="inlineStr"/>
       <c r="L146" s="7" t="inlineStr"/>
-      <c r="M146" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M146" s="7" t="inlineStr"/>
       <c r="N146" s="6" t="n">
         <v>1</v>
       </c>
@@ -7060,7 +7060,7 @@
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 47</t>
+          <t>Сотрудник 54</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -7116,7 +7116,7 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 20</t>
+          <t>Сотрудник 3</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -7413,7 +7413,7 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 45</t>
+          <t>Сотрудник 38</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 38</t>
+          <t>Сотрудник 45</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 19</t>
+          <t>Сотрудник 47</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E173" s="6" t="n">
@@ -8041,8 +8041,12 @@
       <c r="K173" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L173" s="7" t="inlineStr"/>
-      <c r="M173" s="7" t="inlineStr"/>
+      <c r="L173" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N173" s="7" t="inlineStr"/>
       <c r="O173" s="7" t="inlineStr"/>
       <c r="P173" s="7" t="inlineStr"/>
@@ -8054,12 +8058,12 @@
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 50</t>
+          <t>Сотрудник 20</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -8069,7 +8073,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
@@ -8079,12 +8083,8 @@
       <c r="I174" s="7" t="inlineStr"/>
       <c r="J174" s="7" t="inlineStr"/>
       <c r="K174" s="7" t="inlineStr"/>
-      <c r="L174" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M174" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L174" s="7" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
       <c r="N174" s="6" t="n">
         <v>1</v>
       </c>
@@ -8255,12 +8255,12 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E179" s="6" t="n">
@@ -8284,8 +8284,12 @@
       <c r="K179" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L179" s="7" t="inlineStr"/>
-      <c r="M179" s="7" t="inlineStr"/>
+      <c r="L179" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N179" s="7" t="inlineStr"/>
       <c r="O179" s="7" t="inlineStr"/>
       <c r="P179" s="7" t="inlineStr"/>
@@ -8297,7 +8301,7 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 44</t>
+          <t>Сотрудник 31</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -8307,12 +8311,12 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E180" s="6" t="n">
@@ -8336,8 +8340,12 @@
       <c r="K180" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L180" s="7" t="inlineStr"/>
-      <c r="M180" s="7" t="inlineStr"/>
+      <c r="L180" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N180" s="7" t="inlineStr"/>
       <c r="O180" s="7" t="inlineStr"/>
       <c r="P180" s="7" t="inlineStr"/>
@@ -8359,12 +8367,12 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E181" s="6" t="n">
@@ -8391,9 +8399,7 @@
       <c r="L181" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M181" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M181" s="7" t="inlineStr"/>
       <c r="N181" s="7" t="inlineStr"/>
       <c r="O181" s="7" t="inlineStr"/>
       <c r="P181" s="7" t="inlineStr"/>
@@ -8415,12 +8421,12 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr"/>
@@ -8445,7 +8451,9 @@
       <c r="L182" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M182" s="7" t="inlineStr"/>
+      <c r="M182" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N182" s="7" t="inlineStr"/>
       <c r="O182" s="7" t="inlineStr"/>
       <c r="P182" s="7" t="inlineStr"/>
@@ -8597,7 +8605,7 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 1</t>
+          <t>Сотрудник 43</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -8658,7 +8666,7 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
@@ -8668,7 +8676,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr"/>
@@ -8678,9 +8686,7 @@
       <c r="I187" s="7" t="inlineStr"/>
       <c r="J187" s="7" t="inlineStr"/>
       <c r="K187" s="7" t="inlineStr"/>
-      <c r="L187" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L187" s="7" t="inlineStr"/>
       <c r="M187" s="6" t="n">
         <v>1</v>
       </c>
@@ -8709,12 +8715,12 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 43</t>
+          <t>Сотрудник 11</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
@@ -8724,7 +8730,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr"/>
@@ -8734,12 +8740,8 @@
       <c r="I188" s="7" t="inlineStr"/>
       <c r="J188" s="7" t="inlineStr"/>
       <c r="K188" s="7" t="inlineStr"/>
-      <c r="L188" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M188" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L188" s="7" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
       <c r="N188" s="6" t="n">
         <v>1</v>
       </c>
@@ -8765,12 +8767,12 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 4</t>
+          <t>Сотрудник 14</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
@@ -8780,7 +8782,7 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr"/>
@@ -8791,9 +8793,7 @@
       <c r="J189" s="7" t="inlineStr"/>
       <c r="K189" s="7" t="inlineStr"/>
       <c r="L189" s="7" t="inlineStr"/>
-      <c r="M189" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M189" s="7" t="inlineStr"/>
       <c r="N189" s="6" t="n">
         <v>1</v>
       </c>
@@ -8819,7 +8819,7 @@
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 11</t>
+          <t>Сотрудник 44</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
@@ -9050,7 +9050,7 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 31</t>
+          <t>Сотрудник 19</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E196" s="6" t="n">
@@ -9092,9 +9092,7 @@
       <c r="L196" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M196" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M196" s="7" t="inlineStr"/>
       <c r="N196" s="7" t="inlineStr"/>
       <c r="O196" s="7" t="inlineStr"/>
       <c r="P196" s="7" t="inlineStr"/>
@@ -9106,12 +9104,12 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 3</t>
+          <t>Сотрудник 50</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -9121,7 +9119,7 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr"/>
@@ -9132,7 +9130,9 @@
       <c r="J197" s="7" t="inlineStr"/>
       <c r="K197" s="7" t="inlineStr"/>
       <c r="L197" s="7" t="inlineStr"/>
-      <c r="M197" s="7" t="inlineStr"/>
+      <c r="M197" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N197" s="6" t="n">
         <v>1</v>
       </c>
@@ -9293,7 +9293,7 @@
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 59</t>
+          <t>Сотрудник 2</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E202" s="6" t="n">
@@ -9332,8 +9332,12 @@
       <c r="K202" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L202" s="7" t="inlineStr"/>
-      <c r="M202" s="7" t="inlineStr"/>
+      <c r="L202" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N202" s="7" t="inlineStr"/>
       <c r="O202" s="7" t="inlineStr"/>
       <c r="P202" s="7" t="inlineStr"/>
@@ -9345,12 +9349,12 @@
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 7</t>
+          <t>Сотрудник 11</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
@@ -9360,7 +9364,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr"/>
@@ -9370,12 +9374,8 @@
       <c r="I203" s="7" t="inlineStr"/>
       <c r="J203" s="7" t="inlineStr"/>
       <c r="K203" s="7" t="inlineStr"/>
-      <c r="L203" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M203" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L203" s="7" t="inlineStr"/>
+      <c r="M203" s="7" t="inlineStr"/>
       <c r="N203" s="6" t="n">
         <v>1</v>
       </c>
@@ -9536,7 +9536,7 @@
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 1</t>
+          <t>Сотрудник 32</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
@@ -9592,7 +9592,7 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 32</t>
+          <t>Сотрудник 28</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
@@ -9648,7 +9648,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 51</t>
+          <t>Сотрудник 22</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
@@ -9694,7 +9694,7 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 22</t>
+          <t>Сотрудник 45</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -10508,7 +10508,7 @@
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 8</t>
+          <t>Сотрудник 7</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
@@ -10562,7 +10562,7 @@
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 52</t>
+          <t>Сотрудник 8</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
@@ -10618,7 +10618,7 @@
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 28</t>
+          <t>Сотрудник 1</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -10762,7 +10762,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 14</t>
+          <t>Сотрудник 52</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 11</t>
+          <t>Сотрудник 4</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -11203,7 +11203,7 @@
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 2</t>
+          <t>Сотрудник 15</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
@@ -11486,7 +11486,7 @@
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 1</t>
+          <t>Сотрудник 54</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E253" s="6" t="n">
@@ -11516,11 +11516,21 @@
       <c r="H253" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I253" s="7" t="inlineStr"/>
-      <c r="J253" s="7" t="inlineStr"/>
-      <c r="K253" s="7" t="inlineStr"/>
-      <c r="L253" s="7" t="inlineStr"/>
-      <c r="M253" s="7" t="inlineStr"/>
+      <c r="I253" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N253" s="7" t="inlineStr"/>
       <c r="O253" s="7" t="inlineStr"/>
       <c r="P253" s="7" t="inlineStr"/>
@@ -11532,237 +11542,233 @@
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 64</t>
+          <t>Сотрудник 33</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr"/>
       <c r="F254" s="7" t="inlineStr"/>
       <c r="G254" s="7" t="inlineStr"/>
       <c r="H254" s="7" t="inlineStr"/>
-      <c r="I254" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J254" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K254" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I254" s="7" t="inlineStr"/>
+      <c r="J254" s="7" t="inlineStr"/>
+      <c r="K254" s="7" t="inlineStr"/>
       <c r="L254" s="7" t="inlineStr"/>
       <c r="M254" s="7" t="inlineStr"/>
-      <c r="N254" s="7" t="inlineStr"/>
-      <c r="O254" s="7" t="inlineStr"/>
-      <c r="P254" s="7" t="inlineStr"/>
-      <c r="Q254" s="7" t="inlineStr"/>
-      <c r="R254" s="7" t="inlineStr"/>
-      <c r="S254" s="7" t="inlineStr"/>
-      <c r="T254" s="7" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 19</t>
-        </is>
-      </c>
-      <c r="B255" s="5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C255" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>9,00</t>
-        </is>
-      </c>
-      <c r="E255" s="7" t="inlineStr"/>
-      <c r="F255" s="7" t="inlineStr"/>
-      <c r="G255" s="7" t="inlineStr"/>
-      <c r="H255" s="7" t="inlineStr"/>
-      <c r="I255" s="7" t="inlineStr"/>
-      <c r="J255" s="7" t="inlineStr"/>
-      <c r="K255" s="7" t="inlineStr"/>
-      <c r="L255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S255" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T255" s="6" t="n">
-        <v>1</v>
+      <c r="N254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S254" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T254" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Суббота · 02.05.2026</t>
+        </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="inlineStr">
-        <is>
-          <t>Суббота · 02.05.2026</t>
-        </is>
-      </c>
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>ПРИЛАВОК</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n"/>
+      <c r="C257" s="3" t="n"/>
+      <c r="D257" s="3" t="n"/>
+      <c r="E257" s="3" t="n"/>
+      <c r="F257" s="3" t="n"/>
+      <c r="G257" s="3" t="n"/>
+      <c r="H257" s="3" t="n"/>
+      <c r="I257" s="3" t="n"/>
+      <c r="J257" s="3" t="n"/>
+      <c r="K257" s="3" t="n"/>
+      <c r="L257" s="3" t="n"/>
+      <c r="M257" s="3" t="n"/>
+      <c r="N257" s="3" t="n"/>
+      <c r="O257" s="3" t="n"/>
+      <c r="P257" s="3" t="n"/>
+      <c r="Q257" s="3" t="n"/>
+      <c r="R257" s="3" t="n"/>
+      <c r="S257" s="3" t="n"/>
+      <c r="T257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>ПРИЛАВОК</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="n"/>
-      <c r="C258" s="3" t="n"/>
-      <c r="D258" s="3" t="n"/>
-      <c r="E258" s="3" t="n"/>
-      <c r="F258" s="3" t="n"/>
-      <c r="G258" s="3" t="n"/>
-      <c r="H258" s="3" t="n"/>
-      <c r="I258" s="3" t="n"/>
-      <c r="J258" s="3" t="n"/>
-      <c r="K258" s="3" t="n"/>
-      <c r="L258" s="3" t="n"/>
-      <c r="M258" s="3" t="n"/>
-      <c r="N258" s="3" t="n"/>
-      <c r="O258" s="3" t="n"/>
-      <c r="P258" s="3" t="n"/>
-      <c r="Q258" s="3" t="n"/>
-      <c r="R258" s="3" t="n"/>
-      <c r="S258" s="3" t="n"/>
-      <c r="T258" s="3" t="n"/>
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J258" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O258" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P258" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q258" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R258" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S258" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T258" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G259" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H259" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J259" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K259" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L259" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M259" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N259" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O259" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P259" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q259" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R259" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S259" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T259" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 15</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E259" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G259" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" s="7" t="inlineStr"/>
+      <c r="I259" s="7" t="inlineStr"/>
+      <c r="J259" s="7" t="inlineStr"/>
+      <c r="K259" s="7" t="inlineStr"/>
+      <c r="L259" s="7" t="inlineStr"/>
+      <c r="M259" s="7" t="inlineStr"/>
+      <c r="N259" s="7" t="inlineStr"/>
+      <c r="O259" s="7" t="inlineStr"/>
+      <c r="P259" s="7" t="inlineStr"/>
+      <c r="Q259" s="7" t="inlineStr"/>
+      <c r="R259" s="7" t="inlineStr"/>
+      <c r="S259" s="7" t="inlineStr"/>
+      <c r="T259" s="7" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -11772,30 +11778,32 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E260" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr"/>
       <c r="F260" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H260" s="7" t="inlineStr"/>
-      <c r="I260" s="7" t="inlineStr"/>
+      <c r="H260" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I260" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J260" s="7" t="inlineStr"/>
       <c r="K260" s="7" t="inlineStr"/>
       <c r="L260" s="7" t="inlineStr"/>
@@ -11811,38 +11819,36 @@
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 14</t>
+          <t>Сотрудник 16</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr"/>
-      <c r="F261" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G261" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F261" s="7" t="inlineStr"/>
+      <c r="G261" s="7" t="inlineStr"/>
       <c r="H261" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I261" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J261" s="7" t="inlineStr"/>
+      <c r="J261" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="K261" s="7" t="inlineStr"/>
       <c r="L261" s="7" t="inlineStr"/>
       <c r="M261" s="7" t="inlineStr"/>
@@ -11857,42 +11863,52 @@
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 16</t>
+          <t>Сотрудник 68</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr"/>
       <c r="F262" s="7" t="inlineStr"/>
       <c r="G262" s="7" t="inlineStr"/>
-      <c r="H262" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H262" s="7" t="inlineStr"/>
       <c r="I262" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J262" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K262" s="7" t="inlineStr"/>
-      <c r="L262" s="7" t="inlineStr"/>
-      <c r="M262" s="7" t="inlineStr"/>
-      <c r="N262" s="7" t="inlineStr"/>
-      <c r="O262" s="7" t="inlineStr"/>
-      <c r="P262" s="7" t="inlineStr"/>
+      <c r="K262" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P262" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q262" s="7" t="inlineStr"/>
       <c r="R262" s="7" t="inlineStr"/>
       <c r="S262" s="7" t="inlineStr"/>
@@ -11901,31 +11917,29 @@
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 68</t>
+          <t>Сотрудник 37</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr"/>
       <c r="F263" s="7" t="inlineStr"/>
       <c r="G263" s="7" t="inlineStr"/>
       <c r="H263" s="7" t="inlineStr"/>
-      <c r="I263" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I263" s="7" t="inlineStr"/>
       <c r="J263" s="6" t="n">
         <v>1</v>
       </c>
@@ -11935,18 +11949,10 @@
       <c r="L263" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M263" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N263" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O263" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P263" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M263" s="7" t="inlineStr"/>
+      <c r="N263" s="7" t="inlineStr"/>
+      <c r="O263" s="7" t="inlineStr"/>
+      <c r="P263" s="7" t="inlineStr"/>
       <c r="Q263" s="7" t="inlineStr"/>
       <c r="R263" s="7" t="inlineStr"/>
       <c r="S263" s="7" t="inlineStr"/>
@@ -11955,22 +11961,22 @@
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 37</t>
+          <t>Сотрудник 9</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E264" s="7" t="inlineStr"/>
@@ -11978,17 +11984,19 @@
       <c r="G264" s="7" t="inlineStr"/>
       <c r="H264" s="7" t="inlineStr"/>
       <c r="I264" s="7" t="inlineStr"/>
-      <c r="J264" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="J264" s="7" t="inlineStr"/>
       <c r="K264" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L264" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M264" s="7" t="inlineStr"/>
-      <c r="N264" s="7" t="inlineStr"/>
+      <c r="M264" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N264" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="O264" s="7" t="inlineStr"/>
       <c r="P264" s="7" t="inlineStr"/>
       <c r="Q264" s="7" t="inlineStr"/>
@@ -11999,7 +12007,7 @@
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 9</t>
+          <t>Сотрудник 18</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
@@ -12045,22 +12053,22 @@
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 18</t>
+          <t>Сотрудник 25</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E266" s="7" t="inlineStr"/>
@@ -12069,19 +12077,17 @@
       <c r="H266" s="7" t="inlineStr"/>
       <c r="I266" s="7" t="inlineStr"/>
       <c r="J266" s="7" t="inlineStr"/>
-      <c r="K266" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L266" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K266" s="7" t="inlineStr"/>
+      <c r="L266" s="7" t="inlineStr"/>
       <c r="M266" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N266" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O266" s="7" t="inlineStr"/>
+      <c r="O266" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="P266" s="7" t="inlineStr"/>
       <c r="Q266" s="7" t="inlineStr"/>
       <c r="R266" s="7" t="inlineStr"/>
@@ -12091,22 +12097,22 @@
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 25</t>
+          <t>Сотрудник 30</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>6,00</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr"/>
@@ -12117,25 +12123,31 @@
       <c r="J267" s="7" t="inlineStr"/>
       <c r="K267" s="7" t="inlineStr"/>
       <c r="L267" s="7" t="inlineStr"/>
-      <c r="M267" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N267" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M267" s="7" t="inlineStr"/>
+      <c r="N267" s="7" t="inlineStr"/>
       <c r="O267" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P267" s="7" t="inlineStr"/>
-      <c r="Q267" s="7" t="inlineStr"/>
-      <c r="R267" s="7" t="inlineStr"/>
-      <c r="S267" s="7" t="inlineStr"/>
-      <c r="T267" s="7" t="inlineStr"/>
+      <c r="P267" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q267" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R267" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S267" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T267" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 30</t>
+          <t>Сотрудник 42</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -12145,12 +12157,12 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr"/>
@@ -12172,30 +12184,24 @@
       <c r="Q268" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R268" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S268" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T268" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R268" s="7" t="inlineStr"/>
+      <c r="S268" s="7" t="inlineStr"/>
+      <c r="T268" s="7" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 42</t>
+          <t>Сотрудник 29</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
@@ -12213,38 +12219,38 @@
       <c r="L269" s="7" t="inlineStr"/>
       <c r="M269" s="7" t="inlineStr"/>
       <c r="N269" s="7" t="inlineStr"/>
-      <c r="O269" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="O269" s="7" t="inlineStr"/>
       <c r="P269" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q269" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R269" s="7" t="inlineStr"/>
+      <c r="R269" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S269" s="7" t="inlineStr"/>
       <c r="T269" s="7" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 55</t>
+          <t>Сотрудник 6</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr"/>
@@ -12258,27 +12264,29 @@
       <c r="M270" s="7" t="inlineStr"/>
       <c r="N270" s="7" t="inlineStr"/>
       <c r="O270" s="7" t="inlineStr"/>
-      <c r="P270" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="P270" s="7" t="inlineStr"/>
       <c r="Q270" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R270" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="S270" s="7" t="inlineStr"/>
-      <c r="T270" s="7" t="inlineStr"/>
+      <c r="S270" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T270" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 6</t>
+          <t>Сотрудник 50</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
@@ -12288,7 +12296,7 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr"/>
@@ -12303,9 +12311,7 @@
       <c r="N271" s="7" t="inlineStr"/>
       <c r="O271" s="7" t="inlineStr"/>
       <c r="P271" s="7" t="inlineStr"/>
-      <c r="Q271" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q271" s="7" t="inlineStr"/>
       <c r="R271" s="6" t="n">
         <v>1</v>
       </c>
@@ -12316,199 +12322,199 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 50</t>
-        </is>
-      </c>
-      <c r="B272" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C272" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>Суббота · 02.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>КАРТОФЕЛЬ</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n"/>
+      <c r="C274" s="3" t="n"/>
+      <c r="D274" s="3" t="n"/>
+      <c r="E274" s="3" t="n"/>
+      <c r="F274" s="3" t="n"/>
+      <c r="G274" s="3" t="n"/>
+      <c r="H274" s="3" t="n"/>
+      <c r="I274" s="3" t="n"/>
+      <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
+      <c r="L274" s="3" t="n"/>
+      <c r="M274" s="3" t="n"/>
+      <c r="N274" s="3" t="n"/>
+      <c r="O274" s="3" t="n"/>
+      <c r="P274" s="3" t="n"/>
+      <c r="Q274" s="3" t="n"/>
+      <c r="R274" s="3" t="n"/>
+      <c r="S274" s="3" t="n"/>
+      <c r="T274" s="3" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M275" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N275" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O275" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P275" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q275" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R275" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S275" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T275" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 2</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
         <is>
           <t>3,00</t>
         </is>
       </c>
-      <c r="E272" s="7" t="inlineStr"/>
-      <c r="F272" s="7" t="inlineStr"/>
-      <c r="G272" s="7" t="inlineStr"/>
-      <c r="H272" s="7" t="inlineStr"/>
-      <c r="I272" s="7" t="inlineStr"/>
-      <c r="J272" s="7" t="inlineStr"/>
-      <c r="K272" s="7" t="inlineStr"/>
-      <c r="L272" s="7" t="inlineStr"/>
-      <c r="M272" s="7" t="inlineStr"/>
-      <c r="N272" s="7" t="inlineStr"/>
-      <c r="O272" s="7" t="inlineStr"/>
-      <c r="P272" s="7" t="inlineStr"/>
-      <c r="Q272" s="7" t="inlineStr"/>
-      <c r="R272" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S272" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T272" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="1" t="inlineStr">
-        <is>
-          <t>Суббота · 02.05.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>КАРТОФЕЛЬ</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="n"/>
-      <c r="C275" s="3" t="n"/>
-      <c r="D275" s="3" t="n"/>
-      <c r="E275" s="3" t="n"/>
-      <c r="F275" s="3" t="n"/>
-      <c r="G275" s="3" t="n"/>
-      <c r="H275" s="3" t="n"/>
-      <c r="I275" s="3" t="n"/>
-      <c r="J275" s="3" t="n"/>
-      <c r="K275" s="3" t="n"/>
-      <c r="L275" s="3" t="n"/>
-      <c r="M275" s="3" t="n"/>
-      <c r="N275" s="3" t="n"/>
-      <c r="O275" s="3" t="n"/>
-      <c r="P275" s="3" t="n"/>
-      <c r="Q275" s="3" t="n"/>
-      <c r="R275" s="3" t="n"/>
-      <c r="S275" s="3" t="n"/>
-      <c r="T275" s="3" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D276" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E276" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F276" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G276" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H276" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I276" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J276" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K276" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L276" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M276" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N276" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O276" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P276" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q276" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R276" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S276" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T276" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="E276" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" s="7" t="inlineStr"/>
+      <c r="I276" s="7" t="inlineStr"/>
+      <c r="J276" s="7" t="inlineStr"/>
+      <c r="K276" s="7" t="inlineStr"/>
+      <c r="L276" s="7" t="inlineStr"/>
+      <c r="M276" s="7" t="inlineStr"/>
+      <c r="N276" s="7" t="inlineStr"/>
+      <c r="O276" s="7" t="inlineStr"/>
+      <c r="P276" s="7" t="inlineStr"/>
+      <c r="Q276" s="7" t="inlineStr"/>
+      <c r="R276" s="7" t="inlineStr"/>
+      <c r="S276" s="7" t="inlineStr"/>
+      <c r="T276" s="7" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 47</t>
+          <t>Сотрудник 48</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>9:00</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -12516,17 +12522,17 @@
           <t>3,00</t>
         </is>
       </c>
-      <c r="E277" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F277" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E277" s="7" t="inlineStr"/>
+      <c r="F277" s="7" t="inlineStr"/>
       <c r="G277" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H277" s="7" t="inlineStr"/>
-      <c r="I277" s="7" t="inlineStr"/>
+      <c r="H277" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J277" s="7" t="inlineStr"/>
       <c r="K277" s="7" t="inlineStr"/>
       <c r="L277" s="7" t="inlineStr"/>
@@ -12542,17 +12548,17 @@
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 48</t>
+          <t>Сотрудник 60</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -12563,17 +12569,17 @@
       <c r="E278" s="7" t="inlineStr"/>
       <c r="F278" s="7" t="inlineStr"/>
       <c r="G278" s="7" t="inlineStr"/>
-      <c r="H278" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I278" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H278" s="7" t="inlineStr"/>
+      <c r="I278" s="7" t="inlineStr"/>
       <c r="J278" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K278" s="7" t="inlineStr"/>
-      <c r="L278" s="7" t="inlineStr"/>
+      <c r="K278" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M278" s="7" t="inlineStr"/>
       <c r="N278" s="7" t="inlineStr"/>
       <c r="O278" s="7" t="inlineStr"/>
@@ -12586,22 +12592,22 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 60</t>
+          <t>Сотрудник 19</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr"/>
@@ -12609,217 +12615,225 @@
       <c r="G279" s="7" t="inlineStr"/>
       <c r="H279" s="7" t="inlineStr"/>
       <c r="I279" s="7" t="inlineStr"/>
-      <c r="J279" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K279" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L279" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M279" s="7" t="inlineStr"/>
-      <c r="N279" s="7" t="inlineStr"/>
-      <c r="O279" s="7" t="inlineStr"/>
-      <c r="P279" s="7" t="inlineStr"/>
-      <c r="Q279" s="7" t="inlineStr"/>
-      <c r="R279" s="7" t="inlineStr"/>
-      <c r="S279" s="7" t="inlineStr"/>
-      <c r="T279" s="7" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 33</t>
-        </is>
-      </c>
-      <c r="B280" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C280" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E280" s="7" t="inlineStr"/>
-      <c r="F280" s="7" t="inlineStr"/>
-      <c r="G280" s="7" t="inlineStr"/>
-      <c r="H280" s="7" t="inlineStr"/>
-      <c r="I280" s="7" t="inlineStr"/>
-      <c r="J280" s="7" t="inlineStr"/>
-      <c r="K280" s="7" t="inlineStr"/>
-      <c r="L280" s="7" t="inlineStr"/>
-      <c r="M280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S280" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T280" s="6" t="n">
-        <v>1</v>
+      <c r="J279" s="7" t="inlineStr"/>
+      <c r="K279" s="7" t="inlineStr"/>
+      <c r="L279" s="7" t="inlineStr"/>
+      <c r="M279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S279" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T279" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Суббота · 02.05.2026</t>
+        </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="inlineStr">
-        <is>
-          <t>Суббота · 02.05.2026</t>
-        </is>
-      </c>
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>КУХНЯ</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n"/>
+      <c r="C282" s="3" t="n"/>
+      <c r="D282" s="3" t="n"/>
+      <c r="E282" s="3" t="n"/>
+      <c r="F282" s="3" t="n"/>
+      <c r="G282" s="3" t="n"/>
+      <c r="H282" s="3" t="n"/>
+      <c r="I282" s="3" t="n"/>
+      <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
+      <c r="L282" s="3" t="n"/>
+      <c r="M282" s="3" t="n"/>
+      <c r="N282" s="3" t="n"/>
+      <c r="O282" s="3" t="n"/>
+      <c r="P282" s="3" t="n"/>
+      <c r="Q282" s="3" t="n"/>
+      <c r="R282" s="3" t="n"/>
+      <c r="S282" s="3" t="n"/>
+      <c r="T282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>КУХНЯ</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="n"/>
-      <c r="C283" s="3" t="n"/>
-      <c r="D283" s="3" t="n"/>
-      <c r="E283" s="3" t="n"/>
-      <c r="F283" s="3" t="n"/>
-      <c r="G283" s="3" t="n"/>
-      <c r="H283" s="3" t="n"/>
-      <c r="I283" s="3" t="n"/>
-      <c r="J283" s="3" t="n"/>
-      <c r="K283" s="3" t="n"/>
-      <c r="L283" s="3" t="n"/>
-      <c r="M283" s="3" t="n"/>
-      <c r="N283" s="3" t="n"/>
-      <c r="O283" s="3" t="n"/>
-      <c r="P283" s="3" t="n"/>
-      <c r="Q283" s="3" t="n"/>
-      <c r="R283" s="3" t="n"/>
-      <c r="S283" s="3" t="n"/>
-      <c r="T283" s="3" t="n"/>
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M283" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N283" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O283" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P283" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q283" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R283" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S283" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T283" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B284" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D284" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E284" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F284" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G284" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H284" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J284" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K284" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L284" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M284" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N284" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O284" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P284" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q284" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R284" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S284" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T284" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 17</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>7,00</t>
+        </is>
+      </c>
+      <c r="E284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" s="7" t="inlineStr"/>
+      <c r="M284" s="7" t="inlineStr"/>
+      <c r="N284" s="7" t="inlineStr"/>
+      <c r="O284" s="7" t="inlineStr"/>
+      <c r="P284" s="7" t="inlineStr"/>
+      <c r="Q284" s="7" t="inlineStr"/>
+      <c r="R284" s="7" t="inlineStr"/>
+      <c r="S284" s="7" t="inlineStr"/>
+      <c r="T284" s="7" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 54</t>
+          <t>Сотрудник 59</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -12873,17 +12887,17 @@
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 59</t>
+          <t>Сотрудник 5</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>9:00</t>
         </is>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -12891,12 +12905,8 @@
           <t>7,00</t>
         </is>
       </c>
-      <c r="E286" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F286" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E286" s="7" t="inlineStr"/>
+      <c r="F286" s="7" t="inlineStr"/>
       <c r="G286" s="6" t="n">
         <v>1</v>
       </c>
@@ -12912,8 +12922,12 @@
       <c r="K286" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L286" s="7" t="inlineStr"/>
-      <c r="M286" s="7" t="inlineStr"/>
+      <c r="L286" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N286" s="7" t="inlineStr"/>
       <c r="O286" s="7" t="inlineStr"/>
       <c r="P286" s="7" t="inlineStr"/>
@@ -12925,17 +12939,17 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 5</t>
+          <t>Сотрудник 1</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>9:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -12945,12 +12959,8 @@
       </c>
       <c r="E287" s="7" t="inlineStr"/>
       <c r="F287" s="7" t="inlineStr"/>
-      <c r="G287" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H287" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G287" s="7" t="inlineStr"/>
+      <c r="H287" s="7" t="inlineStr"/>
       <c r="I287" s="6" t="n">
         <v>1</v>
       </c>
@@ -12966,8 +12976,12 @@
       <c r="M287" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N287" s="7" t="inlineStr"/>
-      <c r="O287" s="7" t="inlineStr"/>
+      <c r="N287" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="P287" s="7" t="inlineStr"/>
       <c r="Q287" s="7" t="inlineStr"/>
       <c r="R287" s="7" t="inlineStr"/>
@@ -12977,31 +12991,29 @@
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 7</t>
+          <t>Сотрудник 21</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr"/>
       <c r="F288" s="7" t="inlineStr"/>
       <c r="G288" s="7" t="inlineStr"/>
       <c r="H288" s="7" t="inlineStr"/>
-      <c r="I288" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I288" s="7" t="inlineStr"/>
       <c r="J288" s="6" t="n">
         <v>1</v>
       </c>
@@ -13011,15 +13023,9 @@
       <c r="L288" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M288" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N288" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O288" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M288" s="7" t="inlineStr"/>
+      <c r="N288" s="7" t="inlineStr"/>
+      <c r="O288" s="7" t="inlineStr"/>
       <c r="P288" s="7" t="inlineStr"/>
       <c r="Q288" s="7" t="inlineStr"/>
       <c r="R288" s="7" t="inlineStr"/>
@@ -13034,7 +13040,7 @@
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
@@ -13044,7 +13050,7 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr"/>
@@ -13052,9 +13058,7 @@
       <c r="G289" s="7" t="inlineStr"/>
       <c r="H289" s="7" t="inlineStr"/>
       <c r="I289" s="7" t="inlineStr"/>
-      <c r="J289" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="J289" s="7" t="inlineStr"/>
       <c r="K289" s="6" t="n">
         <v>1</v>
       </c>
@@ -13083,22 +13087,22 @@
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 21</t>
+          <t>Сотрудник 43</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr"/>
@@ -13107,32 +13111,44 @@
       <c r="H290" s="7" t="inlineStr"/>
       <c r="I290" s="7" t="inlineStr"/>
       <c r="J290" s="7" t="inlineStr"/>
-      <c r="K290" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K290" s="7" t="inlineStr"/>
       <c r="L290" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M290" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N290" s="7" t="inlineStr"/>
-      <c r="O290" s="7" t="inlineStr"/>
-      <c r="P290" s="7" t="inlineStr"/>
-      <c r="Q290" s="7" t="inlineStr"/>
-      <c r="R290" s="7" t="inlineStr"/>
-      <c r="S290" s="7" t="inlineStr"/>
-      <c r="T290" s="7" t="inlineStr"/>
+      <c r="N290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T290" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 43</t>
+          <t>Сотрудник 4</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
@@ -13142,7 +13158,7 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr"/>
@@ -13152,9 +13168,7 @@
       <c r="I291" s="7" t="inlineStr"/>
       <c r="J291" s="7" t="inlineStr"/>
       <c r="K291" s="7" t="inlineStr"/>
-      <c r="L291" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L291" s="7" t="inlineStr"/>
       <c r="M291" s="6" t="n">
         <v>1</v>
       </c>
@@ -13183,7 +13197,7 @@
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 17</t>
+          <t>Сотрудник 11</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -13237,7 +13251,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 66</t>
+          <t>Сотрудник 44</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -13291,7 +13305,7 @@
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 4</t>
+          <t>Сотрудник 31</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -13340,237 +13354,233 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 15</t>
-        </is>
-      </c>
-      <c r="B295" s="5" t="inlineStr">
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>Суббота · 02.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>ЗАЛ</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="n"/>
+      <c r="C297" s="3" t="n"/>
+      <c r="D297" s="3" t="n"/>
+      <c r="E297" s="3" t="n"/>
+      <c r="F297" s="3" t="n"/>
+      <c r="G297" s="3" t="n"/>
+      <c r="H297" s="3" t="n"/>
+      <c r="I297" s="3" t="n"/>
+      <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
+      <c r="L297" s="3" t="n"/>
+      <c r="M297" s="3" t="n"/>
+      <c r="N297" s="3" t="n"/>
+      <c r="O297" s="3" t="n"/>
+      <c r="P297" s="3" t="n"/>
+      <c r="Q297" s="3" t="n"/>
+      <c r="R297" s="3" t="n"/>
+      <c r="S297" s="3" t="n"/>
+      <c r="T297" s="3" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G298" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M298" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N298" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O298" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P298" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q298" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R298" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S298" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T298" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 14</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E295" s="7" t="inlineStr"/>
-      <c r="F295" s="7" t="inlineStr"/>
-      <c r="G295" s="7" t="inlineStr"/>
-      <c r="H295" s="7" t="inlineStr"/>
-      <c r="I295" s="7" t="inlineStr"/>
-      <c r="J295" s="7" t="inlineStr"/>
-      <c r="K295" s="7" t="inlineStr"/>
-      <c r="L295" s="7" t="inlineStr"/>
-      <c r="M295" s="7" t="inlineStr"/>
-      <c r="N295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S295" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T295" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="inlineStr">
-        <is>
-          <t>Суббота · 02.05.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>ЗАЛ</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="n"/>
-      <c r="C298" s="3" t="n"/>
-      <c r="D298" s="3" t="n"/>
-      <c r="E298" s="3" t="n"/>
-      <c r="F298" s="3" t="n"/>
-      <c r="G298" s="3" t="n"/>
-      <c r="H298" s="3" t="n"/>
-      <c r="I298" s="3" t="n"/>
-      <c r="J298" s="3" t="n"/>
-      <c r="K298" s="3" t="n"/>
-      <c r="L298" s="3" t="n"/>
-      <c r="M298" s="3" t="n"/>
-      <c r="N298" s="3" t="n"/>
-      <c r="O298" s="3" t="n"/>
-      <c r="P298" s="3" t="n"/>
-      <c r="Q298" s="3" t="n"/>
-      <c r="R298" s="3" t="n"/>
-      <c r="S298" s="3" t="n"/>
-      <c r="T298" s="3" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D299" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E299" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F299" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G299" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H299" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I299" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J299" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K299" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L299" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M299" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N299" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O299" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P299" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q299" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R299" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S299" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T299" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>9,00</t>
+        </is>
+      </c>
+      <c r="E299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N299" s="7" t="inlineStr"/>
+      <c r="O299" s="7" t="inlineStr"/>
+      <c r="P299" s="7" t="inlineStr"/>
+      <c r="Q299" s="7" t="inlineStr"/>
+      <c r="R299" s="7" t="inlineStr"/>
+      <c r="S299" s="7" t="inlineStr"/>
+      <c r="T299" s="7" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 2</t>
+          <t>Сотрудник 51</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E300" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F300" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G300" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H300" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I300" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J300" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E300" s="7" t="inlineStr"/>
+      <c r="F300" s="7" t="inlineStr"/>
+      <c r="G300" s="7" t="inlineStr"/>
+      <c r="H300" s="7" t="inlineStr"/>
+      <c r="I300" s="7" t="inlineStr"/>
+      <c r="J300" s="7" t="inlineStr"/>
       <c r="K300" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L300" s="7" t="inlineStr"/>
-      <c r="M300" s="7" t="inlineStr"/>
+      <c r="L300" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M300" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N300" s="7" t="inlineStr"/>
       <c r="O300" s="7" t="inlineStr"/>
       <c r="P300" s="7" t="inlineStr"/>
@@ -13582,17 +13592,17 @@
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 51</t>
+          <t>Сотрудник 10</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -13606,18 +13616,18 @@
       <c r="H301" s="7" t="inlineStr"/>
       <c r="I301" s="7" t="inlineStr"/>
       <c r="J301" s="7" t="inlineStr"/>
-      <c r="K301" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L301" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M301" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N301" s="7" t="inlineStr"/>
-      <c r="O301" s="7" t="inlineStr"/>
-      <c r="P301" s="7" t="inlineStr"/>
+      <c r="K301" s="7" t="inlineStr"/>
+      <c r="L301" s="7" t="inlineStr"/>
+      <c r="M301" s="7" t="inlineStr"/>
+      <c r="N301" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O301" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P301" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q301" s="7" t="inlineStr"/>
       <c r="R301" s="7" t="inlineStr"/>
       <c r="S301" s="7" t="inlineStr"/>
@@ -13626,12 +13636,12 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 52</t>
+          <t>Сотрудник 66</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
@@ -13641,7 +13651,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr"/>
@@ -13651,12 +13661,8 @@
       <c r="I302" s="7" t="inlineStr"/>
       <c r="J302" s="7" t="inlineStr"/>
       <c r="K302" s="7" t="inlineStr"/>
-      <c r="L302" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M302" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L302" s="7" t="inlineStr"/>
+      <c r="M302" s="7" t="inlineStr"/>
       <c r="N302" s="6" t="n">
         <v>1</v>
       </c>
@@ -13679,541 +13685,561 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 10</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E303" s="7" t="inlineStr"/>
-      <c r="F303" s="7" t="inlineStr"/>
-      <c r="G303" s="7" t="inlineStr"/>
-      <c r="H303" s="7" t="inlineStr"/>
-      <c r="I303" s="7" t="inlineStr"/>
-      <c r="J303" s="7" t="inlineStr"/>
-      <c r="K303" s="7" t="inlineStr"/>
-      <c r="L303" s="7" t="inlineStr"/>
-      <c r="M303" s="7" t="inlineStr"/>
-      <c r="N303" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O303" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P303" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q303" s="7" t="inlineStr"/>
-      <c r="R303" s="7" t="inlineStr"/>
-      <c r="S303" s="7" t="inlineStr"/>
-      <c r="T303" s="7" t="inlineStr"/>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>Воскресенье · 03.05.2026</t>
+        </is>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="inlineStr">
-        <is>
-          <t>Воскресенье · 03.05.2026</t>
-        </is>
-      </c>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>НАПИТКИ</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n"/>
+      <c r="C305" s="3" t="n"/>
+      <c r="D305" s="3" t="n"/>
+      <c r="E305" s="3" t="n"/>
+      <c r="F305" s="3" t="n"/>
+      <c r="G305" s="3" t="n"/>
+      <c r="H305" s="3" t="n"/>
+      <c r="I305" s="3" t="n"/>
+      <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="n"/>
+      <c r="L305" s="3" t="n"/>
+      <c r="M305" s="3" t="n"/>
+      <c r="N305" s="3" t="n"/>
+      <c r="O305" s="3" t="n"/>
+      <c r="P305" s="3" t="n"/>
+      <c r="Q305" s="3" t="n"/>
+      <c r="R305" s="3" t="n"/>
+      <c r="S305" s="3" t="n"/>
+      <c r="T305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>НАПИТКИ</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="n"/>
-      <c r="C306" s="3" t="n"/>
-      <c r="D306" s="3" t="n"/>
-      <c r="E306" s="3" t="n"/>
-      <c r="F306" s="3" t="n"/>
-      <c r="G306" s="3" t="n"/>
-      <c r="H306" s="3" t="n"/>
-      <c r="I306" s="3" t="n"/>
-      <c r="J306" s="3" t="n"/>
-      <c r="K306" s="3" t="n"/>
-      <c r="L306" s="3" t="n"/>
-      <c r="M306" s="3" t="n"/>
-      <c r="N306" s="3" t="n"/>
-      <c r="O306" s="3" t="n"/>
-      <c r="P306" s="3" t="n"/>
-      <c r="Q306" s="3" t="n"/>
-      <c r="R306" s="3" t="n"/>
-      <c r="S306" s="3" t="n"/>
-      <c r="T306" s="3" t="n"/>
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I306" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J306" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K306" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N306" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O306" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P306" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q306" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R306" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S306" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T306" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="307">
-      <c r="A307" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B307" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C307" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D307" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E307" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F307" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G307" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H307" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I307" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J307" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K307" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L307" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M307" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N307" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O307" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P307" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q307" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R307" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S307" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T307" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 4</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>7,00</t>
+        </is>
+      </c>
+      <c r="E307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" s="7" t="inlineStr"/>
+      <c r="M307" s="7" t="inlineStr"/>
+      <c r="N307" s="7" t="inlineStr"/>
+      <c r="O307" s="7" t="inlineStr"/>
+      <c r="P307" s="7" t="inlineStr"/>
+      <c r="Q307" s="7" t="inlineStr"/>
+      <c r="R307" s="7" t="inlineStr"/>
+      <c r="S307" s="7" t="inlineStr"/>
+      <c r="T307" s="7" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 54</t>
+          <t>Сотрудник 47</t>
         </is>
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E308" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F308" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G308" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>9,00</t>
+        </is>
+      </c>
+      <c r="E308" s="7" t="inlineStr"/>
+      <c r="F308" s="7" t="inlineStr"/>
+      <c r="G308" s="7" t="inlineStr"/>
       <c r="H308" s="7" t="inlineStr"/>
       <c r="I308" s="7" t="inlineStr"/>
       <c r="J308" s="7" t="inlineStr"/>
       <c r="K308" s="7" t="inlineStr"/>
-      <c r="L308" s="7" t="inlineStr"/>
-      <c r="M308" s="7" t="inlineStr"/>
-      <c r="N308" s="7" t="inlineStr"/>
-      <c r="O308" s="7" t="inlineStr"/>
-      <c r="P308" s="7" t="inlineStr"/>
-      <c r="Q308" s="7" t="inlineStr"/>
-      <c r="R308" s="7" t="inlineStr"/>
-      <c r="S308" s="7" t="inlineStr"/>
-      <c r="T308" s="7" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 38</t>
-        </is>
-      </c>
-      <c r="B309" s="5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C309" s="5" t="inlineStr">
+      <c r="L308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S308" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T308" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>Воскресенье · 03.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>ПРИЛАВОК</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="n"/>
+      <c r="C311" s="3" t="n"/>
+      <c r="D311" s="3" t="n"/>
+      <c r="E311" s="3" t="n"/>
+      <c r="F311" s="3" t="n"/>
+      <c r="G311" s="3" t="n"/>
+      <c r="H311" s="3" t="n"/>
+      <c r="I311" s="3" t="n"/>
+      <c r="J311" s="3" t="n"/>
+      <c r="K311" s="3" t="n"/>
+      <c r="L311" s="3" t="n"/>
+      <c r="M311" s="3" t="n"/>
+      <c r="N311" s="3" t="n"/>
+      <c r="O311" s="3" t="n"/>
+      <c r="P311" s="3" t="n"/>
+      <c r="Q311" s="3" t="n"/>
+      <c r="R311" s="3" t="n"/>
+      <c r="S311" s="3" t="n"/>
+      <c r="T311" s="3" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H312" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I312" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O312" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P312" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q312" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R312" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S312" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T312" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 13</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E313" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" s="7" t="inlineStr"/>
+      <c r="J313" s="7" t="inlineStr"/>
+      <c r="K313" s="7" t="inlineStr"/>
+      <c r="L313" s="7" t="inlineStr"/>
+      <c r="M313" s="7" t="inlineStr"/>
+      <c r="N313" s="7" t="inlineStr"/>
+      <c r="O313" s="7" t="inlineStr"/>
+      <c r="P313" s="7" t="inlineStr"/>
+      <c r="Q313" s="7" t="inlineStr"/>
+      <c r="R313" s="7" t="inlineStr"/>
+      <c r="S313" s="7" t="inlineStr"/>
+      <c r="T313" s="7" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 16</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>9:00</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E314" s="7" t="inlineStr"/>
+      <c r="F314" s="7" t="inlineStr"/>
+      <c r="G314" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I314" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K314" s="7" t="inlineStr"/>
+      <c r="L314" s="7" t="inlineStr"/>
+      <c r="M314" s="7" t="inlineStr"/>
+      <c r="N314" s="7" t="inlineStr"/>
+      <c r="O314" s="7" t="inlineStr"/>
+      <c r="P314" s="7" t="inlineStr"/>
+      <c r="Q314" s="7" t="inlineStr"/>
+      <c r="R314" s="7" t="inlineStr"/>
+      <c r="S314" s="7" t="inlineStr"/>
+      <c r="T314" s="7" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 68</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D309" s="5" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E309" s="7" t="inlineStr"/>
-      <c r="F309" s="7" t="inlineStr"/>
-      <c r="G309" s="7" t="inlineStr"/>
-      <c r="H309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N309" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O309" s="7" t="inlineStr"/>
-      <c r="P309" s="7" t="inlineStr"/>
-      <c r="Q309" s="7" t="inlineStr"/>
-      <c r="R309" s="7" t="inlineStr"/>
-      <c r="S309" s="7" t="inlineStr"/>
-      <c r="T309" s="7" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 0</t>
-        </is>
-      </c>
-      <c r="B310" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C310" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E310" s="7" t="inlineStr"/>
-      <c r="F310" s="7" t="inlineStr"/>
-      <c r="G310" s="7" t="inlineStr"/>
-      <c r="H310" s="7" t="inlineStr"/>
-      <c r="I310" s="7" t="inlineStr"/>
-      <c r="J310" s="7" t="inlineStr"/>
-      <c r="K310" s="7" t="inlineStr"/>
-      <c r="L310" s="7" t="inlineStr"/>
-      <c r="M310" s="7" t="inlineStr"/>
-      <c r="N310" s="7" t="inlineStr"/>
-      <c r="O310" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P310" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q310" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R310" s="7" t="inlineStr"/>
-      <c r="S310" s="7" t="inlineStr"/>
-      <c r="T310" s="7" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 36</t>
-        </is>
-      </c>
-      <c r="B311" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C311" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D311" s="5" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E311" s="7" t="inlineStr"/>
-      <c r="F311" s="7" t="inlineStr"/>
-      <c r="G311" s="7" t="inlineStr"/>
-      <c r="H311" s="7" t="inlineStr"/>
-      <c r="I311" s="7" t="inlineStr"/>
-      <c r="J311" s="7" t="inlineStr"/>
-      <c r="K311" s="7" t="inlineStr"/>
-      <c r="L311" s="7" t="inlineStr"/>
-      <c r="M311" s="7" t="inlineStr"/>
-      <c r="N311" s="7" t="inlineStr"/>
-      <c r="O311" s="7" t="inlineStr"/>
-      <c r="P311" s="7" t="inlineStr"/>
-      <c r="Q311" s="7" t="inlineStr"/>
-      <c r="R311" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S311" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T311" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="inlineStr">
-        <is>
-          <t>Воскресенье · 03.05.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>ПРИЛАВОК</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="n"/>
-      <c r="C314" s="3" t="n"/>
-      <c r="D314" s="3" t="n"/>
-      <c r="E314" s="3" t="n"/>
-      <c r="F314" s="3" t="n"/>
-      <c r="G314" s="3" t="n"/>
-      <c r="H314" s="3" t="n"/>
-      <c r="I314" s="3" t="n"/>
-      <c r="J314" s="3" t="n"/>
-      <c r="K314" s="3" t="n"/>
-      <c r="L314" s="3" t="n"/>
-      <c r="M314" s="3" t="n"/>
-      <c r="N314" s="3" t="n"/>
-      <c r="O314" s="3" t="n"/>
-      <c r="P314" s="3" t="n"/>
-      <c r="Q314" s="3" t="n"/>
-      <c r="R314" s="3" t="n"/>
-      <c r="S314" s="3" t="n"/>
-      <c r="T314" s="3" t="n"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B315" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C315" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D315" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E315" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F315" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G315" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H315" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I315" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J315" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K315" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L315" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M315" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N315" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O315" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P315" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q315" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R315" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S315" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T315" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>6,00</t>
+        </is>
+      </c>
+      <c r="E315" s="7" t="inlineStr"/>
+      <c r="F315" s="7" t="inlineStr"/>
+      <c r="G315" s="7" t="inlineStr"/>
+      <c r="H315" s="7" t="inlineStr"/>
+      <c r="I315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N315" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O315" s="7" t="inlineStr"/>
+      <c r="P315" s="7" t="inlineStr"/>
+      <c r="Q315" s="7" t="inlineStr"/>
+      <c r="R315" s="7" t="inlineStr"/>
+      <c r="S315" s="7" t="inlineStr"/>
+      <c r="T315" s="7" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 13</t>
+          <t>Сотрудник 29</t>
         </is>
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="E316" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F316" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G316" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H316" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E316" s="7" t="inlineStr"/>
+      <c r="F316" s="7" t="inlineStr"/>
+      <c r="G316" s="7" t="inlineStr"/>
+      <c r="H316" s="7" t="inlineStr"/>
       <c r="I316" s="7" t="inlineStr"/>
-      <c r="J316" s="7" t="inlineStr"/>
-      <c r="K316" s="7" t="inlineStr"/>
-      <c r="L316" s="7" t="inlineStr"/>
+      <c r="J316" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K316" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L316" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M316" s="7" t="inlineStr"/>
       <c r="N316" s="7" t="inlineStr"/>
       <c r="O316" s="7" t="inlineStr"/>
@@ -14226,17 +14252,17 @@
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 16</t>
+          <t>Сотрудник 63</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>9:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
@@ -14246,19 +14272,19 @@
       </c>
       <c r="E317" s="7" t="inlineStr"/>
       <c r="F317" s="7" t="inlineStr"/>
-      <c r="G317" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H317" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I317" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G317" s="7" t="inlineStr"/>
+      <c r="H317" s="7" t="inlineStr"/>
+      <c r="I317" s="7" t="inlineStr"/>
       <c r="J317" s="7" t="inlineStr"/>
-      <c r="K317" s="7" t="inlineStr"/>
-      <c r="L317" s="7" t="inlineStr"/>
-      <c r="M317" s="7" t="inlineStr"/>
+      <c r="K317" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L317" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M317" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N317" s="7" t="inlineStr"/>
       <c r="O317" s="7" t="inlineStr"/>
       <c r="P317" s="7" t="inlineStr"/>
@@ -14270,37 +14296,31 @@
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 68</t>
+          <t>Сотрудник 6</t>
         </is>
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>6,00</t>
+          <t>9,00</t>
         </is>
       </c>
       <c r="E318" s="7" t="inlineStr"/>
       <c r="F318" s="7" t="inlineStr"/>
       <c r="G318" s="7" t="inlineStr"/>
       <c r="H318" s="7" t="inlineStr"/>
-      <c r="I318" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J318" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K318" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I318" s="7" t="inlineStr"/>
+      <c r="J318" s="7" t="inlineStr"/>
+      <c r="K318" s="7" t="inlineStr"/>
       <c r="L318" s="6" t="n">
         <v>1</v>
       </c>
@@ -14310,32 +14330,44 @@
       <c r="N318" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O318" s="7" t="inlineStr"/>
-      <c r="P318" s="7" t="inlineStr"/>
-      <c r="Q318" s="7" t="inlineStr"/>
-      <c r="R318" s="7" t="inlineStr"/>
-      <c r="S318" s="7" t="inlineStr"/>
-      <c r="T318" s="7" t="inlineStr"/>
+      <c r="O318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T318" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 29</t>
+          <t>Сотрудник 25</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E319" s="7" t="inlineStr"/>
@@ -14343,19 +14375,21 @@
       <c r="G319" s="7" t="inlineStr"/>
       <c r="H319" s="7" t="inlineStr"/>
       <c r="I319" s="7" t="inlineStr"/>
-      <c r="J319" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K319" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L319" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M319" s="7" t="inlineStr"/>
-      <c r="N319" s="7" t="inlineStr"/>
-      <c r="O319" s="7" t="inlineStr"/>
-      <c r="P319" s="7" t="inlineStr"/>
+      <c r="J319" s="7" t="inlineStr"/>
+      <c r="K319" s="7" t="inlineStr"/>
+      <c r="L319" s="7" t="inlineStr"/>
+      <c r="M319" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N319" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O319" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P319" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q319" s="7" t="inlineStr"/>
       <c r="R319" s="7" t="inlineStr"/>
       <c r="S319" s="7" t="inlineStr"/>
@@ -14364,17 +14398,17 @@
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 63</t>
+          <t>Сотрудник 57</t>
         </is>
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -14387,22 +14421,22 @@
       <c r="G320" s="7" t="inlineStr"/>
       <c r="H320" s="7" t="inlineStr"/>
       <c r="I320" s="7" t="inlineStr"/>
-      <c r="J320" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K320" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L320" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M320" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N320" s="7" t="inlineStr"/>
-      <c r="O320" s="7" t="inlineStr"/>
-      <c r="P320" s="7" t="inlineStr"/>
-      <c r="Q320" s="7" t="inlineStr"/>
+      <c r="J320" s="7" t="inlineStr"/>
+      <c r="K320" s="7" t="inlineStr"/>
+      <c r="L320" s="7" t="inlineStr"/>
+      <c r="M320" s="7" t="inlineStr"/>
+      <c r="N320" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O320" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P320" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q320" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R320" s="7" t="inlineStr"/>
       <c r="S320" s="7" t="inlineStr"/>
       <c r="T320" s="7" t="inlineStr"/>
@@ -14410,22 +14444,22 @@
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 6</t>
+          <t>Сотрудник 41</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E321" s="7" t="inlineStr"/>
@@ -14435,15 +14469,9 @@
       <c r="I321" s="7" t="inlineStr"/>
       <c r="J321" s="7" t="inlineStr"/>
       <c r="K321" s="7" t="inlineStr"/>
-      <c r="L321" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M321" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N321" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L321" s="7" t="inlineStr"/>
+      <c r="M321" s="7" t="inlineStr"/>
+      <c r="N321" s="7" t="inlineStr"/>
       <c r="O321" s="6" t="n">
         <v>1</v>
       </c>
@@ -14453,30 +14481,24 @@
       <c r="Q321" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R321" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S321" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T321" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R321" s="7" t="inlineStr"/>
+      <c r="S321" s="7" t="inlineStr"/>
+      <c r="T321" s="7" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 25</t>
+          <t>Сотрудник 36</t>
         </is>
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -14492,42 +14514,42 @@
       <c r="J322" s="7" t="inlineStr"/>
       <c r="K322" s="7" t="inlineStr"/>
       <c r="L322" s="7" t="inlineStr"/>
-      <c r="M322" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N322" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O322" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P322" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q322" s="7" t="inlineStr"/>
-      <c r="R322" s="7" t="inlineStr"/>
-      <c r="S322" s="7" t="inlineStr"/>
-      <c r="T322" s="7" t="inlineStr"/>
+      <c r="M322" s="7" t="inlineStr"/>
+      <c r="N322" s="7" t="inlineStr"/>
+      <c r="O322" s="7" t="inlineStr"/>
+      <c r="P322" s="7" t="inlineStr"/>
+      <c r="Q322" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R322" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S322" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T322" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 57</t>
+          <t>Сотрудник 19</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E323" s="7" t="inlineStr"/>
@@ -14539,577 +14561,597 @@
       <c r="K323" s="7" t="inlineStr"/>
       <c r="L323" s="7" t="inlineStr"/>
       <c r="M323" s="7" t="inlineStr"/>
-      <c r="N323" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O323" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P323" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q323" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R323" s="7" t="inlineStr"/>
-      <c r="S323" s="7" t="inlineStr"/>
-      <c r="T323" s="7" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 41</t>
-        </is>
-      </c>
-      <c r="B324" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C324" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E324" s="7" t="inlineStr"/>
-      <c r="F324" s="7" t="inlineStr"/>
-      <c r="G324" s="7" t="inlineStr"/>
-      <c r="H324" s="7" t="inlineStr"/>
-      <c r="I324" s="7" t="inlineStr"/>
-      <c r="J324" s="7" t="inlineStr"/>
-      <c r="K324" s="7" t="inlineStr"/>
-      <c r="L324" s="7" t="inlineStr"/>
-      <c r="M324" s="7" t="inlineStr"/>
-      <c r="N324" s="7" t="inlineStr"/>
-      <c r="O324" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P324" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q324" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R324" s="7" t="inlineStr"/>
-      <c r="S324" s="7" t="inlineStr"/>
-      <c r="T324" s="7" t="inlineStr"/>
+      <c r="N323" s="7" t="inlineStr"/>
+      <c r="O323" s="7" t="inlineStr"/>
+      <c r="P323" s="7" t="inlineStr"/>
+      <c r="Q323" s="7" t="inlineStr"/>
+      <c r="R323" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S323" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T323" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 4</t>
-        </is>
-      </c>
-      <c r="B325" s="5" t="inlineStr">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>Воскресенье · 03.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>КАРТОФЕЛЬ</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="n"/>
+      <c r="C326" s="3" t="n"/>
+      <c r="D326" s="3" t="n"/>
+      <c r="E326" s="3" t="n"/>
+      <c r="F326" s="3" t="n"/>
+      <c r="G326" s="3" t="n"/>
+      <c r="H326" s="3" t="n"/>
+      <c r="I326" s="3" t="n"/>
+      <c r="J326" s="3" t="n"/>
+      <c r="K326" s="3" t="n"/>
+      <c r="L326" s="3" t="n"/>
+      <c r="M326" s="3" t="n"/>
+      <c r="N326" s="3" t="n"/>
+      <c r="O326" s="3" t="n"/>
+      <c r="P326" s="3" t="n"/>
+      <c r="Q326" s="3" t="n"/>
+      <c r="R326" s="3" t="n"/>
+      <c r="S326" s="3" t="n"/>
+      <c r="T326" s="3" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H327" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I327" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J327" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K327" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L327" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M327" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N327" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O327" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P327" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q327" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R327" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S327" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T327" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 2</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>8,00</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L328" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M328" s="7" t="inlineStr"/>
+      <c r="N328" s="7" t="inlineStr"/>
+      <c r="O328" s="7" t="inlineStr"/>
+      <c r="P328" s="7" t="inlineStr"/>
+      <c r="Q328" s="7" t="inlineStr"/>
+      <c r="R328" s="7" t="inlineStr"/>
+      <c r="S328" s="7" t="inlineStr"/>
+      <c r="T328" s="7" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 33</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>8,00</t>
+        </is>
+      </c>
+      <c r="E329" s="7" t="inlineStr"/>
+      <c r="F329" s="7" t="inlineStr"/>
+      <c r="G329" s="7" t="inlineStr"/>
+      <c r="H329" s="7" t="inlineStr"/>
+      <c r="I329" s="7" t="inlineStr"/>
+      <c r="J329" s="7" t="inlineStr"/>
+      <c r="K329" s="7" t="inlineStr"/>
+      <c r="L329" s="7" t="inlineStr"/>
+      <c r="M329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S329" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T329" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>Воскресенье · 03.05.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>КУХНЯ</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="n"/>
+      <c r="C332" s="3" t="n"/>
+      <c r="D332" s="3" t="n"/>
+      <c r="E332" s="3" t="n"/>
+      <c r="F332" s="3" t="n"/>
+      <c r="G332" s="3" t="n"/>
+      <c r="H332" s="3" t="n"/>
+      <c r="I332" s="3" t="n"/>
+      <c r="J332" s="3" t="n"/>
+      <c r="K332" s="3" t="n"/>
+      <c r="L332" s="3" t="n"/>
+      <c r="M332" s="3" t="n"/>
+      <c r="N332" s="3" t="n"/>
+      <c r="O332" s="3" t="n"/>
+      <c r="P332" s="3" t="n"/>
+      <c r="Q332" s="3" t="n"/>
+      <c r="R332" s="3" t="n"/>
+      <c r="S332" s="3" t="n"/>
+      <c r="T332" s="3" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H333" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J333" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L333" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M333" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N333" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O333" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P333" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q333" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R333" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S333" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T333" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 14</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>9,00</t>
+        </is>
+      </c>
+      <c r="E334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M334" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N334" s="7" t="inlineStr"/>
+      <c r="O334" s="7" t="inlineStr"/>
+      <c r="P334" s="7" t="inlineStr"/>
+      <c r="Q334" s="7" t="inlineStr"/>
+      <c r="R334" s="7" t="inlineStr"/>
+      <c r="S334" s="7" t="inlineStr"/>
+      <c r="T334" s="7" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 44</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>7,00</t>
+        </is>
+      </c>
+      <c r="E335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K335" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L335" s="7" t="inlineStr"/>
+      <c r="M335" s="7" t="inlineStr"/>
+      <c r="N335" s="7" t="inlineStr"/>
+      <c r="O335" s="7" t="inlineStr"/>
+      <c r="P335" s="7" t="inlineStr"/>
+      <c r="Q335" s="7" t="inlineStr"/>
+      <c r="R335" s="7" t="inlineStr"/>
+      <c r="S335" s="7" t="inlineStr"/>
+      <c r="T335" s="7" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 23</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C325" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="E325" s="7" t="inlineStr"/>
-      <c r="F325" s="7" t="inlineStr"/>
-      <c r="G325" s="7" t="inlineStr"/>
-      <c r="H325" s="7" t="inlineStr"/>
-      <c r="I325" s="7" t="inlineStr"/>
-      <c r="J325" s="7" t="inlineStr"/>
-      <c r="K325" s="7" t="inlineStr"/>
-      <c r="L325" s="7" t="inlineStr"/>
-      <c r="M325" s="7" t="inlineStr"/>
-      <c r="N325" s="7" t="inlineStr"/>
-      <c r="O325" s="7" t="inlineStr"/>
-      <c r="P325" s="7" t="inlineStr"/>
-      <c r="Q325" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R325" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S325" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T325" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 11</t>
-        </is>
-      </c>
-      <c r="B326" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C326" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D326" s="5" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="E326" s="7" t="inlineStr"/>
-      <c r="F326" s="7" t="inlineStr"/>
-      <c r="G326" s="7" t="inlineStr"/>
-      <c r="H326" s="7" t="inlineStr"/>
-      <c r="I326" s="7" t="inlineStr"/>
-      <c r="J326" s="7" t="inlineStr"/>
-      <c r="K326" s="7" t="inlineStr"/>
-      <c r="L326" s="7" t="inlineStr"/>
-      <c r="M326" s="7" t="inlineStr"/>
-      <c r="N326" s="7" t="inlineStr"/>
-      <c r="O326" s="7" t="inlineStr"/>
-      <c r="P326" s="7" t="inlineStr"/>
-      <c r="Q326" s="7" t="inlineStr"/>
-      <c r="R326" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S326" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T326" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="inlineStr">
-        <is>
-          <t>Воскресенье · 03.05.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>КАРТОФЕЛЬ</t>
-        </is>
-      </c>
-      <c r="B329" s="3" t="n"/>
-      <c r="C329" s="3" t="n"/>
-      <c r="D329" s="3" t="n"/>
-      <c r="E329" s="3" t="n"/>
-      <c r="F329" s="3" t="n"/>
-      <c r="G329" s="3" t="n"/>
-      <c r="H329" s="3" t="n"/>
-      <c r="I329" s="3" t="n"/>
-      <c r="J329" s="3" t="n"/>
-      <c r="K329" s="3" t="n"/>
-      <c r="L329" s="3" t="n"/>
-      <c r="M329" s="3" t="n"/>
-      <c r="N329" s="3" t="n"/>
-      <c r="O329" s="3" t="n"/>
-      <c r="P329" s="3" t="n"/>
-      <c r="Q329" s="3" t="n"/>
-      <c r="R329" s="3" t="n"/>
-      <c r="S329" s="3" t="n"/>
-      <c r="T329" s="3" t="n"/>
-    </row>
-    <row r="330">
-      <c r="A330" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B330" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C330" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D330" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E330" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F330" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G330" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H330" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I330" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J330" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K330" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L330" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M330" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N330" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O330" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P330" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q330" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R330" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S330" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T330" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 2</t>
-        </is>
-      </c>
-      <c r="B331" s="5" t="inlineStr">
-        <is>
-          <t>7:00</t>
-        </is>
-      </c>
-      <c r="C331" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="D331" s="5" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L331" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M331" s="7" t="inlineStr"/>
-      <c r="N331" s="7" t="inlineStr"/>
-      <c r="O331" s="7" t="inlineStr"/>
-      <c r="P331" s="7" t="inlineStr"/>
-      <c r="Q331" s="7" t="inlineStr"/>
-      <c r="R331" s="7" t="inlineStr"/>
-      <c r="S331" s="7" t="inlineStr"/>
-      <c r="T331" s="7" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 33</t>
-        </is>
-      </c>
-      <c r="B332" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C332" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D332" s="5" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E332" s="7" t="inlineStr"/>
-      <c r="F332" s="7" t="inlineStr"/>
-      <c r="G332" s="7" t="inlineStr"/>
-      <c r="H332" s="7" t="inlineStr"/>
-      <c r="I332" s="7" t="inlineStr"/>
-      <c r="J332" s="7" t="inlineStr"/>
-      <c r="K332" s="7" t="inlineStr"/>
-      <c r="L332" s="7" t="inlineStr"/>
-      <c r="M332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S332" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T332" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="1" t="inlineStr">
-        <is>
-          <t>Воскресенье · 03.05.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>КУХНЯ</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="n"/>
-      <c r="C335" s="3" t="n"/>
-      <c r="D335" s="3" t="n"/>
-      <c r="E335" s="3" t="n"/>
-      <c r="F335" s="3" t="n"/>
-      <c r="G335" s="3" t="n"/>
-      <c r="H335" s="3" t="n"/>
-      <c r="I335" s="3" t="n"/>
-      <c r="J335" s="3" t="n"/>
-      <c r="K335" s="3" t="n"/>
-      <c r="L335" s="3" t="n"/>
-      <c r="M335" s="3" t="n"/>
-      <c r="N335" s="3" t="n"/>
-      <c r="O335" s="3" t="n"/>
-      <c r="P335" s="3" t="n"/>
-      <c r="Q335" s="3" t="n"/>
-      <c r="R335" s="3" t="n"/>
-      <c r="S335" s="3" t="n"/>
-      <c r="T335" s="3" t="n"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B336" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C336" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D336" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E336" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G336" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H336" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I336" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J336" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K336" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L336" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M336" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N336" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O336" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P336" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q336" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R336" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S336" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T336" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>9,00</t>
+        </is>
+      </c>
+      <c r="E336" s="7" t="inlineStr"/>
+      <c r="F336" s="7" t="inlineStr"/>
+      <c r="G336" s="7" t="inlineStr"/>
+      <c r="H336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P336" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q336" s="7" t="inlineStr"/>
+      <c r="R336" s="7" t="inlineStr"/>
+      <c r="S336" s="7" t="inlineStr"/>
+      <c r="T336" s="7" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 7</t>
+          <t>Сотрудник 65</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E337" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F337" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G337" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H337" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I337" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E337" s="7" t="inlineStr"/>
+      <c r="F337" s="7" t="inlineStr"/>
+      <c r="G337" s="7" t="inlineStr"/>
+      <c r="H337" s="7" t="inlineStr"/>
+      <c r="I337" s="7" t="inlineStr"/>
       <c r="J337" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K337" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L337" s="7" t="inlineStr"/>
+      <c r="L337" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M337" s="7" t="inlineStr"/>
       <c r="N337" s="7" t="inlineStr"/>
       <c r="O337" s="7" t="inlineStr"/>
@@ -15122,17 +15164,17 @@
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 31</t>
+          <t>Сотрудник 56</t>
         </is>
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
@@ -15140,33 +15182,33 @@
           <t>7,00</t>
         </is>
       </c>
-      <c r="E338" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F338" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G338" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H338" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I338" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J338" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E338" s="7" t="inlineStr"/>
+      <c r="F338" s="7" t="inlineStr"/>
+      <c r="G338" s="7" t="inlineStr"/>
+      <c r="H338" s="7" t="inlineStr"/>
+      <c r="I338" s="7" t="inlineStr"/>
+      <c r="J338" s="7" t="inlineStr"/>
       <c r="K338" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L338" s="7" t="inlineStr"/>
-      <c r="M338" s="7" t="inlineStr"/>
-      <c r="N338" s="7" t="inlineStr"/>
-      <c r="O338" s="7" t="inlineStr"/>
-      <c r="P338" s="7" t="inlineStr"/>
-      <c r="Q338" s="7" t="inlineStr"/>
+      <c r="L338" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M338" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N338" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O338" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P338" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q338" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="R338" s="7" t="inlineStr"/>
       <c r="S338" s="7" t="inlineStr"/>
       <c r="T338" s="7" t="inlineStr"/>
@@ -15174,17 +15216,17 @@
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 23</t>
+          <t>Сотрудник 1</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
@@ -15195,18 +15237,10 @@
       <c r="E339" s="7" t="inlineStr"/>
       <c r="F339" s="7" t="inlineStr"/>
       <c r="G339" s="7" t="inlineStr"/>
-      <c r="H339" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I339" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J339" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K339" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H339" s="7" t="inlineStr"/>
+      <c r="I339" s="7" t="inlineStr"/>
+      <c r="J339" s="7" t="inlineStr"/>
+      <c r="K339" s="7" t="inlineStr"/>
       <c r="L339" s="6" t="n">
         <v>1</v>
       </c>
@@ -15222,30 +15256,38 @@
       <c r="P339" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q339" s="7" t="inlineStr"/>
-      <c r="R339" s="7" t="inlineStr"/>
-      <c r="S339" s="7" t="inlineStr"/>
-      <c r="T339" s="7" t="inlineStr"/>
+      <c r="Q339" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R339" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S339" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T339" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 65</t>
+          <t>Сотрудник 7</t>
         </is>
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E340" s="7" t="inlineStr"/>
@@ -15253,43 +15295,53 @@
       <c r="G340" s="7" t="inlineStr"/>
       <c r="H340" s="7" t="inlineStr"/>
       <c r="I340" s="7" t="inlineStr"/>
-      <c r="J340" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K340" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L340" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M340" s="7" t="inlineStr"/>
-      <c r="N340" s="7" t="inlineStr"/>
-      <c r="O340" s="7" t="inlineStr"/>
-      <c r="P340" s="7" t="inlineStr"/>
-      <c r="Q340" s="7" t="inlineStr"/>
-      <c r="R340" s="7" t="inlineStr"/>
-      <c r="S340" s="7" t="inlineStr"/>
-      <c r="T340" s="7" t="inlineStr"/>
+      <c r="J340" s="7" t="inlineStr"/>
+      <c r="K340" s="7" t="inlineStr"/>
+      <c r="L340" s="7" t="inlineStr"/>
+      <c r="M340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S340" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T340" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 67</t>
+          <t>Сотрудник 66</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>8,00</t>
         </is>
       </c>
       <c r="E341" s="7" t="inlineStr"/>
@@ -15298,32 +15350,42 @@
       <c r="H341" s="7" t="inlineStr"/>
       <c r="I341" s="7" t="inlineStr"/>
       <c r="J341" s="7" t="inlineStr"/>
-      <c r="K341" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L341" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K341" s="7" t="inlineStr"/>
+      <c r="L341" s="7" t="inlineStr"/>
       <c r="M341" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N341" s="7" t="inlineStr"/>
-      <c r="O341" s="7" t="inlineStr"/>
-      <c r="P341" s="7" t="inlineStr"/>
-      <c r="Q341" s="7" t="inlineStr"/>
-      <c r="R341" s="7" t="inlineStr"/>
-      <c r="S341" s="7" t="inlineStr"/>
-      <c r="T341" s="7" t="inlineStr"/>
+      <c r="N341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S341" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T341" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 1</t>
+          <t>Сотрудник 15</t>
         </is>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
@@ -15333,7 +15395,7 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>7,00</t>
         </is>
       </c>
       <c r="E342" s="7" t="inlineStr"/>
@@ -15343,12 +15405,8 @@
       <c r="I342" s="7" t="inlineStr"/>
       <c r="J342" s="7" t="inlineStr"/>
       <c r="K342" s="7" t="inlineStr"/>
-      <c r="L342" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M342" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L342" s="7" t="inlineStr"/>
+      <c r="M342" s="7" t="inlineStr"/>
       <c r="N342" s="6" t="n">
         <v>1</v>
       </c>
@@ -15374,12 +15432,12 @@
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 14</t>
+          <t>Сотрудник 11</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
@@ -15389,7 +15447,7 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E343" s="7" t="inlineStr"/>
@@ -15399,24 +15457,12 @@
       <c r="I343" s="7" t="inlineStr"/>
       <c r="J343" s="7" t="inlineStr"/>
       <c r="K343" s="7" t="inlineStr"/>
-      <c r="L343" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M343" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N343" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O343" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P343" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q343" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L343" s="7" t="inlineStr"/>
+      <c r="M343" s="7" t="inlineStr"/>
+      <c r="N343" s="7" t="inlineStr"/>
+      <c r="O343" s="7" t="inlineStr"/>
+      <c r="P343" s="7" t="inlineStr"/>
+      <c r="Q343" s="7" t="inlineStr"/>
       <c r="R343" s="6" t="n">
         <v>1</v>
       </c>
@@ -15427,348 +15473,314 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 15</t>
-        </is>
-      </c>
-      <c r="B344" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C344" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D344" s="5" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E344" s="7" t="inlineStr"/>
-      <c r="F344" s="7" t="inlineStr"/>
-      <c r="G344" s="7" t="inlineStr"/>
-      <c r="H344" s="7" t="inlineStr"/>
-      <c r="I344" s="7" t="inlineStr"/>
-      <c r="J344" s="7" t="inlineStr"/>
-      <c r="K344" s="7" t="inlineStr"/>
-      <c r="L344" s="7" t="inlineStr"/>
-      <c r="M344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T344" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="345">
-      <c r="A345" s="5" t="inlineStr">
-        <is>
-          <t>Сотрудник 66</t>
-        </is>
-      </c>
-      <c r="B345" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C345" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D345" s="5" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E345" s="7" t="inlineStr"/>
-      <c r="F345" s="7" t="inlineStr"/>
-      <c r="G345" s="7" t="inlineStr"/>
-      <c r="H345" s="7" t="inlineStr"/>
-      <c r="I345" s="7" t="inlineStr"/>
-      <c r="J345" s="7" t="inlineStr"/>
-      <c r="K345" s="7" t="inlineStr"/>
-      <c r="L345" s="7" t="inlineStr"/>
-      <c r="M345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S345" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T345" s="6" t="n">
-        <v>1</v>
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>Воскресенье · 03.05.2026</t>
+        </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="5" t="inlineStr">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>ЗАЛ</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="n"/>
+      <c r="C346" s="3" t="n"/>
+      <c r="D346" s="3" t="n"/>
+      <c r="E346" s="3" t="n"/>
+      <c r="F346" s="3" t="n"/>
+      <c r="G346" s="3" t="n"/>
+      <c r="H346" s="3" t="n"/>
+      <c r="I346" s="3" t="n"/>
+      <c r="J346" s="3" t="n"/>
+      <c r="K346" s="3" t="n"/>
+      <c r="L346" s="3" t="n"/>
+      <c r="M346" s="3" t="n"/>
+      <c r="N346" s="3" t="n"/>
+      <c r="O346" s="3" t="n"/>
+      <c r="P346" s="3" t="n"/>
+      <c r="Q346" s="3" t="n"/>
+      <c r="R346" s="3" t="n"/>
+      <c r="S346" s="3" t="n"/>
+      <c r="T346" s="3" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Начало</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>Окончание</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>Длина</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H347" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I347" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J347" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K347" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L347" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M347" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N347" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O347" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P347" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q347" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R347" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S347" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T347" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="inlineStr">
         <is>
           <t>Сотрудник 59</t>
         </is>
       </c>
-      <c r="B346" s="5" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C346" s="5" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="D346" s="5" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E346" s="7" t="inlineStr"/>
-      <c r="F346" s="7" t="inlineStr"/>
-      <c r="G346" s="7" t="inlineStr"/>
-      <c r="H346" s="7" t="inlineStr"/>
-      <c r="I346" s="7" t="inlineStr"/>
-      <c r="J346" s="7" t="inlineStr"/>
-      <c r="K346" s="7" t="inlineStr"/>
-      <c r="L346" s="7" t="inlineStr"/>
-      <c r="M346" s="7" t="inlineStr"/>
-      <c r="N346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S346" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T346" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="inlineStr">
-        <is>
-          <t>Воскресенье · 03.05.2026</t>
-        </is>
-      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>7:00</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E348" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" s="7" t="inlineStr"/>
+      <c r="I348" s="7" t="inlineStr"/>
+      <c r="J348" s="7" t="inlineStr"/>
+      <c r="K348" s="7" t="inlineStr"/>
+      <c r="L348" s="7" t="inlineStr"/>
+      <c r="M348" s="7" t="inlineStr"/>
+      <c r="N348" s="7" t="inlineStr"/>
+      <c r="O348" s="7" t="inlineStr"/>
+      <c r="P348" s="7" t="inlineStr"/>
+      <c r="Q348" s="7" t="inlineStr"/>
+      <c r="R348" s="7" t="inlineStr"/>
+      <c r="S348" s="7" t="inlineStr"/>
+      <c r="T348" s="7" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>ЗАЛ</t>
-        </is>
-      </c>
-      <c r="B349" s="3" t="n"/>
-      <c r="C349" s="3" t="n"/>
-      <c r="D349" s="3" t="n"/>
-      <c r="E349" s="3" t="n"/>
-      <c r="F349" s="3" t="n"/>
-      <c r="G349" s="3" t="n"/>
-      <c r="H349" s="3" t="n"/>
-      <c r="I349" s="3" t="n"/>
-      <c r="J349" s="3" t="n"/>
-      <c r="K349" s="3" t="n"/>
-      <c r="L349" s="3" t="n"/>
-      <c r="M349" s="3" t="n"/>
-      <c r="N349" s="3" t="n"/>
-      <c r="O349" s="3" t="n"/>
-      <c r="P349" s="3" t="n"/>
-      <c r="Q349" s="3" t="n"/>
-      <c r="R349" s="3" t="n"/>
-      <c r="S349" s="3" t="n"/>
-      <c r="T349" s="3" t="n"/>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 64</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="E349" s="7" t="inlineStr"/>
+      <c r="F349" s="7" t="inlineStr"/>
+      <c r="G349" s="7" t="inlineStr"/>
+      <c r="H349" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I349" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J349" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K349" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L349" s="7" t="inlineStr"/>
+      <c r="M349" s="7" t="inlineStr"/>
+      <c r="N349" s="7" t="inlineStr"/>
+      <c r="O349" s="7" t="inlineStr"/>
+      <c r="P349" s="7" t="inlineStr"/>
+      <c r="Q349" s="7" t="inlineStr"/>
+      <c r="R349" s="7" t="inlineStr"/>
+      <c r="S349" s="7" t="inlineStr"/>
+      <c r="T349" s="7" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="4" t="inlineStr">
-        <is>
-          <t>Сотрудник</t>
-        </is>
-      </c>
-      <c r="B350" s="4" t="inlineStr">
-        <is>
-          <t>Начало</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>Окончание</t>
-        </is>
-      </c>
-      <c r="D350" s="4" t="inlineStr">
-        <is>
-          <t>Длина</t>
-        </is>
-      </c>
-      <c r="E350" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F350" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G350" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H350" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I350" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J350" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K350" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L350" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="M350" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N350" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O350" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P350" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q350" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R350" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S350" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="T350" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t>Сотрудник 67</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E350" s="7" t="inlineStr"/>
+      <c r="F350" s="7" t="inlineStr"/>
+      <c r="G350" s="7" t="inlineStr"/>
+      <c r="H350" s="7" t="inlineStr"/>
+      <c r="I350" s="7" t="inlineStr"/>
+      <c r="J350" s="7" t="inlineStr"/>
+      <c r="K350" s="7" t="inlineStr"/>
+      <c r="L350" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M350" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N350" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O350" s="7" t="inlineStr"/>
+      <c r="P350" s="7" t="inlineStr"/>
+      <c r="Q350" s="7" t="inlineStr"/>
+      <c r="R350" s="7" t="inlineStr"/>
+      <c r="S350" s="7" t="inlineStr"/>
+      <c r="T350" s="7" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 43</t>
+          <t>Сотрудник 62</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J351" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K351" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>3,00</t>
+        </is>
+      </c>
+      <c r="E351" s="7" t="inlineStr"/>
+      <c r="F351" s="7" t="inlineStr"/>
+      <c r="G351" s="7" t="inlineStr"/>
+      <c r="H351" s="7" t="inlineStr"/>
+      <c r="I351" s="7" t="inlineStr"/>
+      <c r="J351" s="7" t="inlineStr"/>
+      <c r="K351" s="7" t="inlineStr"/>
       <c r="L351" s="7" t="inlineStr"/>
       <c r="M351" s="7" t="inlineStr"/>
-      <c r="N351" s="7" t="inlineStr"/>
-      <c r="O351" s="7" t="inlineStr"/>
-      <c r="P351" s="7" t="inlineStr"/>
+      <c r="N351" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O351" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P351" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q351" s="7" t="inlineStr"/>
       <c r="R351" s="7" t="inlineStr"/>
       <c r="S351" s="7" t="inlineStr"/>
@@ -15777,22 +15789,22 @@
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 44</t>
+          <t>Сотрудник 0</t>
         </is>
       </c>
       <c r="B352" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>9,00</t>
+          <t>3,00</t>
         </is>
       </c>
       <c r="E352" s="7" t="inlineStr"/>
@@ -15802,15 +15814,9 @@
       <c r="I352" s="7" t="inlineStr"/>
       <c r="J352" s="7" t="inlineStr"/>
       <c r="K352" s="7" t="inlineStr"/>
-      <c r="L352" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M352" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N352" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L352" s="7" t="inlineStr"/>
+      <c r="M352" s="7" t="inlineStr"/>
+      <c r="N352" s="7" t="inlineStr"/>
       <c r="O352" s="6" t="n">
         <v>1</v>
       </c>
@@ -15820,30 +15826,24 @@
       <c r="Q352" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R352" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S352" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T352" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R352" s="7" t="inlineStr"/>
+      <c r="S352" s="7" t="inlineStr"/>
+      <c r="T352" s="7" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
         <is>
-          <t>Сотрудник 62</t>
+          <t>Сотрудник 54</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D353" s="5" t="inlineStr">
@@ -15860,44 +15860,43 @@
       <c r="K353" s="7" t="inlineStr"/>
       <c r="L353" s="7" t="inlineStr"/>
       <c r="M353" s="7" t="inlineStr"/>
-      <c r="N353" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O353" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P353" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="N353" s="7" t="inlineStr"/>
+      <c r="O353" s="7" t="inlineStr"/>
+      <c r="P353" s="7" t="inlineStr"/>
       <c r="Q353" s="7" t="inlineStr"/>
-      <c r="R353" s="7" t="inlineStr"/>
-      <c r="S353" s="7" t="inlineStr"/>
-      <c r="T353" s="7" t="inlineStr"/>
+      <c r="R353" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S353" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T353" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="35">
     <mergeCell ref="A155:T155"/>
     <mergeCell ref="A229:T229"/>
-    <mergeCell ref="A258:T258"/>
-    <mergeCell ref="A329:T329"/>
     <mergeCell ref="A127:T127"/>
     <mergeCell ref="A143:T143"/>
-    <mergeCell ref="A314:T314"/>
-    <mergeCell ref="A275:T275"/>
+    <mergeCell ref="A257:T257"/>
     <mergeCell ref="A49:T49"/>
-    <mergeCell ref="A349:T349"/>
+    <mergeCell ref="A274:T274"/>
     <mergeCell ref="A94:T94"/>
     <mergeCell ref="A78:T78"/>
-    <mergeCell ref="A283:T283"/>
+    <mergeCell ref="A346:T346"/>
+    <mergeCell ref="A305:T305"/>
     <mergeCell ref="A221:T221"/>
-    <mergeCell ref="A335:T335"/>
     <mergeCell ref="A177:T177"/>
+    <mergeCell ref="A326:T326"/>
+    <mergeCell ref="A282:T282"/>
     <mergeCell ref="A149:T149"/>
+    <mergeCell ref="A332:T332"/>
     <mergeCell ref="A55:T55"/>
-    <mergeCell ref="A306:T306"/>
+    <mergeCell ref="A297:T297"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A251:T251"/>
-    <mergeCell ref="A298:T298"/>
     <mergeCell ref="A194:T194"/>
     <mergeCell ref="A8:T8"/>
     <mergeCell ref="A22:T22"/>
@@ -15906,6 +15905,7 @@
     <mergeCell ref="A100:T100"/>
     <mergeCell ref="A106:T106"/>
     <mergeCell ref="A171:T171"/>
+    <mergeCell ref="A311:T311"/>
     <mergeCell ref="A200:T200"/>
     <mergeCell ref="A43:T43"/>
     <mergeCell ref="A72:T72"/>
